--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251007_201449.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251007_201449.xlsx
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251007_201449.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251007_201449.xlsx
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251007_201449.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251007_201449.xlsx
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251007_201449.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251007_201449.xlsx
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251007_201449.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251007_201449.xlsx
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251007_201449.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251007_201449.xlsx
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
